--- a/Week03/insect_master.xlsx
+++ b/Week03/insect_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishizukakengo/Desktop/gis/Week03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{753BE11E-AB73-1040-9BA2-F1919570898E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F159D7C-1C52-F04A-A216-0EA3C6D4146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>name</t>
   </si>
@@ -69,6 +69,25 @@
   </si>
   <si>
     <t>ミツバチ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ニホンカワウソ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>prefecture</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あああ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>山梨県</t>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ケン </t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -108,7 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,13 +150,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -444,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -453,7 +486,7 @@
     <col min="4" max="4" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,8 +499,13 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -481,7 +519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -495,7 +533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -507,6 +545,17 @@
       </c>
       <c r="D4" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
